--- a/InputData/elec/CDRDfRCP/Cln Dsptchble Rsrc Dmnd for Rlbty Curve Param.xlsx
+++ b/InputData/elec/CDRDfRCP/Cln Dsptchble Rsrc Dmnd for Rlbty Curve Param.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Models\US\Models\eps-us\InputData\elec\CDRDfRCP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\CDRDfRCP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845E5034-0753-4D2F-924A-D8ED6ECB42F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5881D2B-FBBE-4E3A-97DC-892210235A1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7080" yWindow="105" windowWidth="29640" windowHeight="21840" xr2:uid="{DDCF7A3C-4581-48BB-A680-D5CBB461C8EB}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{DDCF7A3C-4581-48BB-A680-D5CBB461C8EB}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>CDRDfRCP Clean Dispatchable Resource Demand for Reliabilty Curve Paramaters</t>
   </si>
@@ -70,6 +70,12 @@
   </si>
   <si>
     <t>Required clena firm</t>
+  </si>
+  <si>
+    <t>We avoid having this increase too sharply in the last few percent of requirement to avoid</t>
+  </si>
+  <si>
+    <t>artificially high CES credit prices in the model.</t>
   </si>
 </sst>
 </file>
@@ -1307,16 +1313,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>14287</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>100012</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>90487</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>176212</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1643,6 +1649,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B207133-CFE8-4DB4-95CD-9BA248AF1C6C}">
   <dimension ref="A1:C63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="11" max="11" width="20.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1674,6 +1683,16 @@
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
